--- a/graphics_manifest v2.xlsx
+++ b/graphics_manifest v2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Others\Development\Chinese Word Games\XiYouHanZiZhan\GitHub_GPT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{47A5CFB5-75F8-4C43-AAC1-A89BAFB091A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E52D2937-1B99-4BFE-8B17-7669C9F5B1BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{99E2F725-6AD6-4F86-8E01-248B0A776BEA}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="996" uniqueCount="685">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="996" uniqueCount="684">
   <si>
     <t>category</t>
   </si>
@@ -298,9 +298,6 @@
     <t>PROVINCE_GENERALS[2] boss</t>
   </si>
   <si>
-    <t>sprites/enemies/generals/02-hunter-liu.webp</t>
-  </si>
-  <si>
     <t>soldier_02</t>
   </si>
   <si>
@@ -313,9 +310,6 @@
     <t>PROVINCE_GENERALS[2] soldier</t>
   </si>
   <si>
-    <t>sprites/enemies/soldiers/02-mountain-guide.webp</t>
-  </si>
-  <si>
     <t>general_03</t>
   </si>
   <si>
@@ -328,9 +322,6 @@
     <t>PROVINCE_GENERALS[3] boss</t>
   </si>
   <si>
-    <t>sprites/enemies/generals/03-general-yin.webp</t>
-  </si>
-  <si>
     <t>soldier_03</t>
   </si>
   <si>
@@ -340,12 +331,6 @@
     <t>Forest Tiger Spirit</t>
   </si>
   <si>
-    <t>PROVINCE_GENERALS[3] soldier</t>
-  </si>
-  <si>
-    <t>sprites/enemies/soldiers/03-forest-tiger-spirit.webp</t>
-  </si>
-  <si>
     <t>general_04</t>
   </si>
   <si>
@@ -2078,6 +2063,18 @@
   </si>
   <si>
     <t>depicting Erlang Shen as a powerful, stern heavenly general with a large head. The defining features are the prominent third 'truth-seeing' eye on his forehead and his strict expression. He wears ornate but muted deep blue and gold armor and a flowing cape. He stands holding his three-pointed double-edged lance (ji).</t>
+  </si>
+  <si>
+    <t>sprites/enemies/soldiers/02-forest-tiger-spirit.webp</t>
+  </si>
+  <si>
+    <t>sprites/enemies/soldiers/03-mountain-guide.webp</t>
+  </si>
+  <si>
+    <t>sprites/enemies/generals/03-hunter-liu.webp</t>
+  </si>
+  <si>
+    <t>sprites/enemies/generals/02-general-yin.webp</t>
   </si>
 </sst>
 </file>
@@ -2976,7 +2973,7 @@
         <v>12</v>
       </c>
       <c r="H2" t="s">
-        <v>676</v>
+        <v>671</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
@@ -3002,7 +2999,7 @@
         <v>19</v>
       </c>
       <c r="H3" t="s">
-        <v>677</v>
+        <v>672</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -3028,7 +3025,7 @@
         <v>19</v>
       </c>
       <c r="H4" t="s">
-        <v>678</v>
+        <v>673</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
@@ -3054,7 +3051,7 @@
         <v>19</v>
       </c>
       <c r="H5" t="s">
-        <v>679</v>
+        <v>674</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
@@ -3080,7 +3077,7 @@
         <v>19</v>
       </c>
       <c r="H6" t="s">
-        <v>680</v>
+        <v>675</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
@@ -3106,7 +3103,7 @@
         <v>19</v>
       </c>
       <c r="H7" t="s">
-        <v>681</v>
+        <v>676</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
@@ -3132,7 +3129,7 @@
         <v>19</v>
       </c>
       <c r="H8" t="s">
-        <v>682</v>
+        <v>677</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
@@ -3158,7 +3155,7 @@
         <v>19</v>
       </c>
       <c r="H9" t="s">
-        <v>683</v>
+        <v>678</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
@@ -3184,7 +3181,7 @@
         <v>19</v>
       </c>
       <c r="H10" t="s">
-        <v>684</v>
+        <v>679</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
@@ -3307,19 +3304,19 @@
         <v>70</v>
       </c>
       <c r="B16" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C16" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="D16" t="s">
+        <v>101</v>
+      </c>
+      <c r="E16" t="s">
         <v>94</v>
       </c>
-      <c r="E16" t="s">
-        <v>95</v>
-      </c>
       <c r="F16" t="s">
-        <v>96</v>
+        <v>680</v>
       </c>
       <c r="G16" t="s">
         <v>76</v>
@@ -3330,19 +3327,19 @@
         <v>70</v>
       </c>
       <c r="B17" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C17" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="D17" t="s">
-        <v>104</v>
+        <v>93</v>
       </c>
       <c r="E17" t="s">
-        <v>105</v>
+        <v>94</v>
       </c>
       <c r="F17" t="s">
-        <v>106</v>
+        <v>681</v>
       </c>
       <c r="G17" t="s">
         <v>76</v>
@@ -3353,19 +3350,19 @@
         <v>70</v>
       </c>
       <c r="B18" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="C18" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="D18" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="E18" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="F18" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="G18" t="s">
         <v>76</v>
@@ -3376,19 +3373,19 @@
         <v>70</v>
       </c>
       <c r="B19" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="C19" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="D19" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="E19" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="F19" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="G19" t="s">
         <v>76</v>
@@ -3399,19 +3396,19 @@
         <v>70</v>
       </c>
       <c r="B20" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="C20" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="D20" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="E20" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="F20" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="G20" t="s">
         <v>76</v>
@@ -3422,19 +3419,19 @@
         <v>70</v>
       </c>
       <c r="B21" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="C21" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="D21" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="E21" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="F21" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="G21" t="s">
         <v>76</v>
@@ -3445,19 +3442,19 @@
         <v>70</v>
       </c>
       <c r="B22" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="C22" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="D22" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="E22" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="F22" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="G22" t="s">
         <v>76</v>
@@ -3468,19 +3465,19 @@
         <v>70</v>
       </c>
       <c r="B23" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="C23" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="D23" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="E23" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="F23" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="G23" t="s">
         <v>76</v>
@@ -3491,19 +3488,19 @@
         <v>70</v>
       </c>
       <c r="B24" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="C24" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="D24" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="E24" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="F24" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="G24" t="s">
         <v>76</v>
@@ -3514,19 +3511,19 @@
         <v>70</v>
       </c>
       <c r="B25" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="C25" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="D25" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="E25" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="F25" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="G25" t="s">
         <v>76</v>
@@ -3537,19 +3534,19 @@
         <v>70</v>
       </c>
       <c r="B26" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="C26" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="D26" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="E26" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="F26" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="G26" t="s">
         <v>76</v>
@@ -3560,19 +3557,19 @@
         <v>70</v>
       </c>
       <c r="B27" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="C27" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="D27" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="E27" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="F27" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="G27" t="s">
         <v>76</v>
@@ -3583,19 +3580,19 @@
         <v>70</v>
       </c>
       <c r="B28" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="C28" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="D28" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="E28" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="F28" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="G28" t="s">
         <v>76</v>
@@ -3606,19 +3603,19 @@
         <v>70</v>
       </c>
       <c r="B29" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="C29" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="D29" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="E29" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="F29" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="G29" t="s">
         <v>76</v>
@@ -3629,19 +3626,19 @@
         <v>70</v>
       </c>
       <c r="B30" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="C30" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="D30" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="E30" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="F30" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="G30" t="s">
         <v>76</v>
@@ -3652,19 +3649,19 @@
         <v>70</v>
       </c>
       <c r="B31" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="C31" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="D31" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="E31" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="F31" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="G31" t="s">
         <v>76</v>
@@ -3675,19 +3672,19 @@
         <v>70</v>
       </c>
       <c r="B32" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="C32" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="D32" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="E32" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="F32" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="G32" t="s">
         <v>76</v>
@@ -3698,19 +3695,19 @@
         <v>70</v>
       </c>
       <c r="B33" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="C33" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="D33" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="E33" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="F33" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="G33" t="s">
         <v>76</v>
@@ -3721,19 +3718,19 @@
         <v>70</v>
       </c>
       <c r="B34" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="C34" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="D34" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="E34" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="F34" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="G34" t="s">
         <v>76</v>
@@ -3744,19 +3741,19 @@
         <v>70</v>
       </c>
       <c r="B35" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="C35" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="D35" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="E35" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="F35" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="G35" t="s">
         <v>76</v>
@@ -3767,19 +3764,19 @@
         <v>70</v>
       </c>
       <c r="B36" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="C36" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="D36" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="E36" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="F36" t="s">
-        <v>288</v>
+        <v>283</v>
       </c>
       <c r="G36" t="s">
         <v>76</v>
@@ -3790,19 +3787,19 @@
         <v>70</v>
       </c>
       <c r="B37" t="s">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="C37" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="D37" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="E37" t="s">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="F37" t="s">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="G37" t="s">
         <v>76</v>
@@ -3813,19 +3810,19 @@
         <v>70</v>
       </c>
       <c r="B38" t="s">
-        <v>304</v>
+        <v>299</v>
       </c>
       <c r="C38" t="s">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="D38" t="s">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="E38" t="s">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="F38" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="G38" t="s">
         <v>76</v>
@@ -3836,19 +3833,19 @@
         <v>70</v>
       </c>
       <c r="B39" t="s">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="C39" t="s">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="D39" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="E39" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="F39" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="G39" t="s">
         <v>76</v>
@@ -3859,19 +3856,19 @@
         <v>70</v>
       </c>
       <c r="B40" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="C40" t="s">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="D40" t="s">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="E40" t="s">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="F40" t="s">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="G40" t="s">
         <v>76</v>
@@ -3882,19 +3879,19 @@
         <v>70</v>
       </c>
       <c r="B41" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="C41" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="D41" t="s">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="E41" t="s">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="F41" t="s">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="G41" t="s">
         <v>76</v>
@@ -3905,19 +3902,19 @@
         <v>70</v>
       </c>
       <c r="B42" t="s">
-        <v>344</v>
+        <v>339</v>
       </c>
       <c r="C42" t="s">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="D42" t="s">
-        <v>346</v>
+        <v>341</v>
       </c>
       <c r="E42" t="s">
-        <v>347</v>
+        <v>342</v>
       </c>
       <c r="F42" t="s">
-        <v>348</v>
+        <v>343</v>
       </c>
       <c r="G42" t="s">
         <v>76</v>
@@ -3928,19 +3925,19 @@
         <v>70</v>
       </c>
       <c r="B43" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="C43" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="D43" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="E43" t="s">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="F43" t="s">
-        <v>358</v>
+        <v>353</v>
       </c>
       <c r="G43" t="s">
         <v>76</v>
@@ -3951,19 +3948,19 @@
         <v>70</v>
       </c>
       <c r="B44" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="C44" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="D44" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="E44" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="F44" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="G44" t="s">
         <v>76</v>
@@ -3974,19 +3971,19 @@
         <v>70</v>
       </c>
       <c r="B45" t="s">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="C45" t="s">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="D45" t="s">
-        <v>376</v>
+        <v>371</v>
       </c>
       <c r="E45" t="s">
-        <v>377</v>
+        <v>372</v>
       </c>
       <c r="F45" t="s">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="G45" t="s">
         <v>76</v>
@@ -3997,19 +3994,19 @@
         <v>70</v>
       </c>
       <c r="B46" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="C46" t="s">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="D46" t="s">
-        <v>386</v>
+        <v>381</v>
       </c>
       <c r="E46" t="s">
-        <v>387</v>
+        <v>382</v>
       </c>
       <c r="F46" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="G46" t="s">
         <v>76</v>
@@ -4020,19 +4017,19 @@
         <v>70</v>
       </c>
       <c r="B47" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="C47" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="D47" t="s">
-        <v>396</v>
+        <v>391</v>
       </c>
       <c r="E47" t="s">
-        <v>397</v>
+        <v>392</v>
       </c>
       <c r="F47" t="s">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="G47" t="s">
         <v>76</v>
@@ -4043,19 +4040,19 @@
         <v>70</v>
       </c>
       <c r="B48" t="s">
-        <v>404</v>
+        <v>399</v>
       </c>
       <c r="C48" t="s">
-        <v>405</v>
+        <v>400</v>
       </c>
       <c r="D48" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="E48" t="s">
-        <v>407</v>
+        <v>402</v>
       </c>
       <c r="F48" t="s">
-        <v>408</v>
+        <v>403</v>
       </c>
       <c r="G48" t="s">
         <v>76</v>
@@ -4066,19 +4063,19 @@
         <v>70</v>
       </c>
       <c r="B49" t="s">
-        <v>414</v>
+        <v>409</v>
       </c>
       <c r="C49" t="s">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="D49" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
       <c r="E49" t="s">
-        <v>417</v>
+        <v>412</v>
       </c>
       <c r="F49" t="s">
-        <v>418</v>
+        <v>413</v>
       </c>
       <c r="G49" t="s">
         <v>76</v>
@@ -4089,19 +4086,19 @@
         <v>70</v>
       </c>
       <c r="B50" t="s">
-        <v>424</v>
+        <v>419</v>
       </c>
       <c r="C50" t="s">
-        <v>425</v>
+        <v>420</v>
       </c>
       <c r="D50" t="s">
-        <v>426</v>
+        <v>421</v>
       </c>
       <c r="E50" t="s">
-        <v>427</v>
+        <v>422</v>
       </c>
       <c r="F50" t="s">
-        <v>428</v>
+        <v>423</v>
       </c>
       <c r="G50" t="s">
         <v>76</v>
@@ -4112,19 +4109,19 @@
         <v>70</v>
       </c>
       <c r="B51" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="C51" t="s">
-        <v>435</v>
+        <v>430</v>
       </c>
       <c r="D51" t="s">
-        <v>436</v>
+        <v>431</v>
       </c>
       <c r="E51" t="s">
-        <v>437</v>
+        <v>432</v>
       </c>
       <c r="F51" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="G51" t="s">
         <v>76</v>
@@ -4135,19 +4132,19 @@
         <v>70</v>
       </c>
       <c r="B52" t="s">
-        <v>444</v>
+        <v>439</v>
       </c>
       <c r="C52" t="s">
-        <v>445</v>
+        <v>440</v>
       </c>
       <c r="D52" t="s">
-        <v>446</v>
+        <v>441</v>
       </c>
       <c r="E52" t="s">
-        <v>447</v>
+        <v>442</v>
       </c>
       <c r="F52" t="s">
-        <v>448</v>
+        <v>443</v>
       </c>
       <c r="G52" t="s">
         <v>76</v>
@@ -4158,19 +4155,19 @@
         <v>70</v>
       </c>
       <c r="B53" t="s">
-        <v>454</v>
+        <v>449</v>
       </c>
       <c r="C53" t="s">
-        <v>455</v>
+        <v>450</v>
       </c>
       <c r="D53" t="s">
-        <v>456</v>
+        <v>451</v>
       </c>
       <c r="E53" t="s">
-        <v>457</v>
+        <v>452</v>
       </c>
       <c r="F53" t="s">
-        <v>458</v>
+        <v>453</v>
       </c>
       <c r="G53" t="s">
         <v>76</v>
@@ -4181,19 +4178,19 @@
         <v>70</v>
       </c>
       <c r="B54" t="s">
-        <v>464</v>
+        <v>459</v>
       </c>
       <c r="C54" t="s">
-        <v>465</v>
+        <v>460</v>
       </c>
       <c r="D54" t="s">
-        <v>466</v>
+        <v>461</v>
       </c>
       <c r="E54" t="s">
-        <v>467</v>
+        <v>462</v>
       </c>
       <c r="F54" t="s">
-        <v>468</v>
+        <v>463</v>
       </c>
       <c r="G54" t="s">
         <v>76</v>
@@ -4204,19 +4201,19 @@
         <v>70</v>
       </c>
       <c r="B55" t="s">
-        <v>474</v>
+        <v>469</v>
       </c>
       <c r="C55" t="s">
-        <v>475</v>
+        <v>470</v>
       </c>
       <c r="D55" t="s">
-        <v>476</v>
+        <v>471</v>
       </c>
       <c r="E55" t="s">
-        <v>477</v>
+        <v>472</v>
       </c>
       <c r="F55" t="s">
-        <v>478</v>
+        <v>473</v>
       </c>
       <c r="G55" t="s">
         <v>76</v>
@@ -4227,19 +4224,19 @@
         <v>70</v>
       </c>
       <c r="B56" t="s">
-        <v>484</v>
+        <v>479</v>
       </c>
       <c r="C56" t="s">
-        <v>485</v>
+        <v>480</v>
       </c>
       <c r="D56" t="s">
-        <v>486</v>
+        <v>481</v>
       </c>
       <c r="E56" t="s">
-        <v>487</v>
+        <v>482</v>
       </c>
       <c r="F56" t="s">
-        <v>488</v>
+        <v>483</v>
       </c>
       <c r="G56" t="s">
         <v>76</v>
@@ -4250,19 +4247,19 @@
         <v>70</v>
       </c>
       <c r="B57" t="s">
-        <v>494</v>
+        <v>489</v>
       </c>
       <c r="C57" t="s">
-        <v>495</v>
+        <v>490</v>
       </c>
       <c r="D57" t="s">
-        <v>496</v>
+        <v>491</v>
       </c>
       <c r="E57" t="s">
-        <v>497</v>
+        <v>492</v>
       </c>
       <c r="F57" t="s">
-        <v>498</v>
+        <v>493</v>
       </c>
       <c r="G57" t="s">
         <v>76</v>
@@ -4273,19 +4270,19 @@
         <v>70</v>
       </c>
       <c r="B58" t="s">
-        <v>504</v>
+        <v>499</v>
       </c>
       <c r="C58" t="s">
-        <v>505</v>
+        <v>500</v>
       </c>
       <c r="D58" t="s">
-        <v>506</v>
+        <v>501</v>
       </c>
       <c r="E58" t="s">
-        <v>507</v>
+        <v>502</v>
       </c>
       <c r="F58" t="s">
-        <v>508</v>
+        <v>503</v>
       </c>
       <c r="G58" t="s">
         <v>76</v>
@@ -4296,19 +4293,19 @@
         <v>70</v>
       </c>
       <c r="B59" t="s">
-        <v>514</v>
+        <v>509</v>
       </c>
       <c r="C59" t="s">
-        <v>515</v>
+        <v>510</v>
       </c>
       <c r="D59" t="s">
-        <v>516</v>
+        <v>511</v>
       </c>
       <c r="E59" t="s">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="F59" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="G59" t="s">
         <v>76</v>
@@ -4319,19 +4316,19 @@
         <v>70</v>
       </c>
       <c r="B60" t="s">
-        <v>524</v>
+        <v>519</v>
       </c>
       <c r="C60" t="s">
-        <v>525</v>
+        <v>520</v>
       </c>
       <c r="D60" t="s">
-        <v>526</v>
+        <v>521</v>
       </c>
       <c r="E60" t="s">
-        <v>527</v>
+        <v>522</v>
       </c>
       <c r="F60" t="s">
-        <v>528</v>
+        <v>523</v>
       </c>
       <c r="G60" t="s">
         <v>76</v>
@@ -4342,19 +4339,19 @@
         <v>70</v>
       </c>
       <c r="B61" t="s">
-        <v>534</v>
+        <v>529</v>
       </c>
       <c r="C61" t="s">
-        <v>535</v>
+        <v>530</v>
       </c>
       <c r="D61" t="s">
-        <v>536</v>
+        <v>531</v>
       </c>
       <c r="E61" t="s">
-        <v>537</v>
+        <v>532</v>
       </c>
       <c r="F61" t="s">
-        <v>538</v>
+        <v>533</v>
       </c>
       <c r="G61" t="s">
         <v>76</v>
@@ -4414,16 +4411,16 @@
         <v>87</v>
       </c>
       <c r="C64" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="D64" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="E64" t="s">
         <v>90</v>
       </c>
       <c r="F64" t="s">
-        <v>91</v>
+        <v>683</v>
       </c>
       <c r="G64" t="s">
         <v>69</v>
@@ -4434,19 +4431,19 @@
         <v>63</v>
       </c>
       <c r="B65" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C65" t="s">
+        <v>88</v>
+      </c>
+      <c r="D65" t="s">
+        <v>89</v>
+      </c>
+      <c r="E65" t="s">
         <v>98</v>
       </c>
-      <c r="D65" t="s">
-        <v>99</v>
-      </c>
-      <c r="E65" t="s">
-        <v>100</v>
-      </c>
       <c r="F65" t="s">
-        <v>101</v>
+        <v>682</v>
       </c>
       <c r="G65" t="s">
         <v>69</v>
@@ -4457,7 +4454,7 @@
         <v>63</v>
       </c>
       <c r="B66" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="C66" t="s">
         <v>21</v>
@@ -4466,10 +4463,10 @@
         <v>22</v>
       </c>
       <c r="E66" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="F66" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="G66" t="s">
         <v>69</v>
@@ -4480,19 +4477,19 @@
         <v>63</v>
       </c>
       <c r="B67" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="C67" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="D67" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="E67" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="F67" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="G67" t="s">
         <v>69</v>
@@ -4503,7 +4500,7 @@
         <v>63</v>
       </c>
       <c r="B68" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="C68" t="s">
         <v>33</v>
@@ -4512,10 +4509,10 @@
         <v>34</v>
       </c>
       <c r="E68" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="F68" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="G68" t="s">
         <v>69</v>
@@ -4526,19 +4523,19 @@
         <v>63</v>
       </c>
       <c r="B69" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="C69" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="D69" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="E69" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="F69" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="G69" t="s">
         <v>69</v>
@@ -4549,19 +4546,19 @@
         <v>63</v>
       </c>
       <c r="B70" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="C70" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="D70" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="E70" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="F70" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="G70" t="s">
         <v>69</v>
@@ -4572,19 +4569,19 @@
         <v>63</v>
       </c>
       <c r="B71" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="C71" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="D71" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="E71" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="F71" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="G71" t="s">
         <v>69</v>
@@ -4595,7 +4592,7 @@
         <v>63</v>
       </c>
       <c r="B72" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="C72" t="s">
         <v>25</v>
@@ -4604,10 +4601,10 @@
         <v>26</v>
       </c>
       <c r="E72" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="F72" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="G72" t="s">
         <v>69</v>
@@ -4618,19 +4615,19 @@
         <v>63</v>
       </c>
       <c r="B73" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="C73" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="D73" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="E73" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="F73" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="G73" t="s">
         <v>69</v>
@@ -4641,7 +4638,7 @@
         <v>63</v>
       </c>
       <c r="B74" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="C74" t="s">
         <v>29</v>
@@ -4650,10 +4647,10 @@
         <v>30</v>
       </c>
       <c r="E74" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="F74" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="G74" t="s">
         <v>69</v>
@@ -4664,19 +4661,19 @@
         <v>63</v>
       </c>
       <c r="B75" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="C75" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="D75" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="E75" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="F75" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="G75" t="s">
         <v>69</v>
@@ -4687,19 +4684,19 @@
         <v>63</v>
       </c>
       <c r="B76" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="C76" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="D76" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="E76" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="F76" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="G76" t="s">
         <v>69</v>
@@ -4710,19 +4707,19 @@
         <v>63</v>
       </c>
       <c r="B77" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="C77" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="D77" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="E77" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="F77" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="G77" t="s">
         <v>69</v>
@@ -4733,19 +4730,19 @@
         <v>63</v>
       </c>
       <c r="B78" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="C78" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="D78" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="E78" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="F78" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="G78" t="s">
         <v>69</v>
@@ -4756,19 +4753,19 @@
         <v>63</v>
       </c>
       <c r="B79" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="C79" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="D79" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="E79" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="F79" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="G79" t="s">
         <v>69</v>
@@ -4779,19 +4776,19 @@
         <v>63</v>
       </c>
       <c r="B80" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="C80" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="D80" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="E80" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="F80" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="G80" t="s">
         <v>69</v>
@@ -4802,19 +4799,19 @@
         <v>63</v>
       </c>
       <c r="B81" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="C81" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="D81" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="E81" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="F81" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="G81" t="s">
         <v>69</v>
@@ -4825,19 +4822,19 @@
         <v>63</v>
       </c>
       <c r="B82" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="C82" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="D82" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="E82" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="F82" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="G82" t="s">
         <v>69</v>
@@ -4848,19 +4845,19 @@
         <v>63</v>
       </c>
       <c r="B83" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="C83" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="D83" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="E83" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="F83" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="G83" t="s">
         <v>69</v>
@@ -4871,19 +4868,19 @@
         <v>63</v>
       </c>
       <c r="B84" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="C84" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="D84" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="E84" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="F84" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="G84" t="s">
         <v>69</v>
@@ -4894,19 +4891,19 @@
         <v>63</v>
       </c>
       <c r="B85" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="C85" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="D85" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="E85" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="F85" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="G85" t="s">
         <v>69</v>
@@ -4917,19 +4914,19 @@
         <v>63</v>
       </c>
       <c r="B86" t="s">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="C86" t="s">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="D86" t="s">
-        <v>301</v>
+        <v>296</v>
       </c>
       <c r="E86" t="s">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="F86" t="s">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="G86" t="s">
         <v>69</v>
@@ -4940,19 +4937,19 @@
         <v>63</v>
       </c>
       <c r="B87" t="s">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="C87" t="s">
-        <v>310</v>
+        <v>305</v>
       </c>
       <c r="D87" t="s">
-        <v>311</v>
+        <v>306</v>
       </c>
       <c r="E87" t="s">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="F87" t="s">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="G87" t="s">
         <v>69</v>
@@ -4963,19 +4960,19 @@
         <v>63</v>
       </c>
       <c r="B88" t="s">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="C88" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="D88" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="E88" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="F88" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="G88" t="s">
         <v>69</v>
@@ -4986,19 +4983,19 @@
         <v>63</v>
       </c>
       <c r="B89" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="C89" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="D89" t="s">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="E89" t="s">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="F89" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="G89" t="s">
         <v>69</v>
@@ -5009,19 +5006,19 @@
         <v>63</v>
       </c>
       <c r="B90" t="s">
-        <v>339</v>
+        <v>334</v>
       </c>
       <c r="C90" t="s">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="D90" t="s">
-        <v>341</v>
+        <v>336</v>
       </c>
       <c r="E90" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="F90" t="s">
-        <v>343</v>
+        <v>338</v>
       </c>
       <c r="G90" t="s">
         <v>69</v>
@@ -5032,19 +5029,19 @@
         <v>63</v>
       </c>
       <c r="B91" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="C91" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="D91" t="s">
-        <v>351</v>
+        <v>346</v>
       </c>
       <c r="E91" t="s">
-        <v>352</v>
+        <v>347</v>
       </c>
       <c r="F91" t="s">
-        <v>353</v>
+        <v>348</v>
       </c>
       <c r="G91" t="s">
         <v>69</v>
@@ -5055,19 +5052,19 @@
         <v>63</v>
       </c>
       <c r="B92" t="s">
-        <v>359</v>
+        <v>354</v>
       </c>
       <c r="C92" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="D92" t="s">
-        <v>361</v>
+        <v>356</v>
       </c>
       <c r="E92" t="s">
-        <v>362</v>
+        <v>357</v>
       </c>
       <c r="F92" t="s">
-        <v>363</v>
+        <v>358</v>
       </c>
       <c r="G92" t="s">
         <v>69</v>
@@ -5078,19 +5075,19 @@
         <v>63</v>
       </c>
       <c r="B93" t="s">
-        <v>369</v>
+        <v>364</v>
       </c>
       <c r="C93" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="D93" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="E93" t="s">
-        <v>372</v>
+        <v>367</v>
       </c>
       <c r="F93" t="s">
-        <v>373</v>
+        <v>368</v>
       </c>
       <c r="G93" t="s">
         <v>69</v>
@@ -5101,19 +5098,19 @@
         <v>63</v>
       </c>
       <c r="B94" t="s">
-        <v>379</v>
+        <v>374</v>
       </c>
       <c r="C94" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="D94" t="s">
-        <v>381</v>
+        <v>376</v>
       </c>
       <c r="E94" t="s">
-        <v>382</v>
+        <v>377</v>
       </c>
       <c r="F94" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="G94" t="s">
         <v>69</v>
@@ -5124,19 +5121,19 @@
         <v>63</v>
       </c>
       <c r="B95" t="s">
-        <v>389</v>
+        <v>384</v>
       </c>
       <c r="C95" t="s">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="D95" t="s">
-        <v>391</v>
+        <v>386</v>
       </c>
       <c r="E95" t="s">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="F95" t="s">
-        <v>393</v>
+        <v>388</v>
       </c>
       <c r="G95" t="s">
         <v>69</v>
@@ -5147,19 +5144,19 @@
         <v>63</v>
       </c>
       <c r="B96" t="s">
-        <v>399</v>
+        <v>394</v>
       </c>
       <c r="C96" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="D96" t="s">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="E96" t="s">
-        <v>402</v>
+        <v>397</v>
       </c>
       <c r="F96" t="s">
-        <v>403</v>
+        <v>398</v>
       </c>
       <c r="G96" t="s">
         <v>69</v>
@@ -5170,19 +5167,19 @@
         <v>63</v>
       </c>
       <c r="B97" t="s">
-        <v>409</v>
+        <v>404</v>
       </c>
       <c r="C97" t="s">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="D97" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="E97" t="s">
-        <v>412</v>
+        <v>407</v>
       </c>
       <c r="F97" t="s">
-        <v>413</v>
+        <v>408</v>
       </c>
       <c r="G97" t="s">
         <v>69</v>
@@ -5193,19 +5190,19 @@
         <v>63</v>
       </c>
       <c r="B98" t="s">
-        <v>419</v>
+        <v>414</v>
       </c>
       <c r="C98" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="D98" t="s">
-        <v>421</v>
+        <v>416</v>
       </c>
       <c r="E98" t="s">
-        <v>422</v>
+        <v>417</v>
       </c>
       <c r="F98" t="s">
-        <v>423</v>
+        <v>418</v>
       </c>
       <c r="G98" t="s">
         <v>69</v>
@@ -5216,19 +5213,19 @@
         <v>63</v>
       </c>
       <c r="B99" t="s">
-        <v>429</v>
+        <v>424</v>
       </c>
       <c r="C99" t="s">
-        <v>430</v>
+        <v>425</v>
       </c>
       <c r="D99" t="s">
-        <v>431</v>
+        <v>426</v>
       </c>
       <c r="E99" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="F99" t="s">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="G99" t="s">
         <v>69</v>
@@ -5239,19 +5236,19 @@
         <v>63</v>
       </c>
       <c r="B100" t="s">
-        <v>439</v>
+        <v>434</v>
       </c>
       <c r="C100" t="s">
-        <v>440</v>
+        <v>435</v>
       </c>
       <c r="D100" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="E100" t="s">
-        <v>442</v>
+        <v>437</v>
       </c>
       <c r="F100" t="s">
-        <v>443</v>
+        <v>438</v>
       </c>
       <c r="G100" t="s">
         <v>69</v>
@@ -5262,19 +5259,19 @@
         <v>63</v>
       </c>
       <c r="B101" t="s">
-        <v>449</v>
+        <v>444</v>
       </c>
       <c r="C101" t="s">
-        <v>450</v>
+        <v>445</v>
       </c>
       <c r="D101" t="s">
-        <v>451</v>
+        <v>446</v>
       </c>
       <c r="E101" t="s">
-        <v>452</v>
+        <v>447</v>
       </c>
       <c r="F101" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="G101" t="s">
         <v>69</v>
@@ -5285,19 +5282,19 @@
         <v>63</v>
       </c>
       <c r="B102" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="C102" t="s">
-        <v>460</v>
+        <v>455</v>
       </c>
       <c r="D102" t="s">
-        <v>461</v>
+        <v>456</v>
       </c>
       <c r="E102" t="s">
-        <v>462</v>
+        <v>457</v>
       </c>
       <c r="F102" t="s">
-        <v>463</v>
+        <v>458</v>
       </c>
       <c r="G102" t="s">
         <v>69</v>
@@ -5308,19 +5305,19 @@
         <v>63</v>
       </c>
       <c r="B103" t="s">
-        <v>469</v>
+        <v>464</v>
       </c>
       <c r="C103" t="s">
-        <v>470</v>
+        <v>465</v>
       </c>
       <c r="D103" t="s">
-        <v>471</v>
+        <v>466</v>
       </c>
       <c r="E103" t="s">
-        <v>472</v>
+        <v>467</v>
       </c>
       <c r="F103" t="s">
-        <v>473</v>
+        <v>468</v>
       </c>
       <c r="G103" t="s">
         <v>69</v>
@@ -5331,19 +5328,19 @@
         <v>63</v>
       </c>
       <c r="B104" t="s">
-        <v>479</v>
+        <v>474</v>
       </c>
       <c r="C104" t="s">
-        <v>480</v>
+        <v>475</v>
       </c>
       <c r="D104" t="s">
-        <v>481</v>
+        <v>476</v>
       </c>
       <c r="E104" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="F104" t="s">
-        <v>483</v>
+        <v>478</v>
       </c>
       <c r="G104" t="s">
         <v>69</v>
@@ -5354,19 +5351,19 @@
         <v>63</v>
       </c>
       <c r="B105" t="s">
-        <v>489</v>
+        <v>484</v>
       </c>
       <c r="C105" t="s">
-        <v>490</v>
+        <v>485</v>
       </c>
       <c r="D105" t="s">
-        <v>491</v>
+        <v>486</v>
       </c>
       <c r="E105" t="s">
-        <v>492</v>
+        <v>487</v>
       </c>
       <c r="F105" t="s">
-        <v>493</v>
+        <v>488</v>
       </c>
       <c r="G105" t="s">
         <v>69</v>
@@ -5377,19 +5374,19 @@
         <v>63</v>
       </c>
       <c r="B106" t="s">
-        <v>499</v>
+        <v>494</v>
       </c>
       <c r="C106" t="s">
-        <v>500</v>
+        <v>495</v>
       </c>
       <c r="D106" t="s">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="E106" t="s">
-        <v>502</v>
+        <v>497</v>
       </c>
       <c r="F106" t="s">
-        <v>503</v>
+        <v>498</v>
       </c>
       <c r="G106" t="s">
         <v>69</v>
@@ -5400,19 +5397,19 @@
         <v>63</v>
       </c>
       <c r="B107" t="s">
-        <v>509</v>
+        <v>504</v>
       </c>
       <c r="C107" t="s">
-        <v>510</v>
+        <v>505</v>
       </c>
       <c r="D107" t="s">
-        <v>511</v>
+        <v>506</v>
       </c>
       <c r="E107" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="F107" t="s">
-        <v>513</v>
+        <v>508</v>
       </c>
       <c r="G107" t="s">
         <v>69</v>
@@ -5423,19 +5420,19 @@
         <v>63</v>
       </c>
       <c r="B108" t="s">
-        <v>519</v>
+        <v>514</v>
       </c>
       <c r="C108" t="s">
-        <v>520</v>
+        <v>515</v>
       </c>
       <c r="D108" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="E108" t="s">
-        <v>522</v>
+        <v>517</v>
       </c>
       <c r="F108" t="s">
-        <v>523</v>
+        <v>518</v>
       </c>
       <c r="G108" t="s">
         <v>69</v>
@@ -5446,19 +5443,19 @@
         <v>63</v>
       </c>
       <c r="B109" t="s">
-        <v>529</v>
+        <v>524</v>
       </c>
       <c r="C109" t="s">
-        <v>530</v>
+        <v>525</v>
       </c>
       <c r="D109" t="s">
-        <v>531</v>
+        <v>526</v>
       </c>
       <c r="E109" t="s">
-        <v>532</v>
+        <v>527</v>
       </c>
       <c r="F109" t="s">
-        <v>533</v>
+        <v>528</v>
       </c>
       <c r="G109" t="s">
         <v>69</v>
@@ -5466,738 +5463,738 @@
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
+        <v>534</v>
+      </c>
+      <c r="B110" t="s">
+        <v>535</v>
+      </c>
+      <c r="C110" t="s">
+        <v>536</v>
+      </c>
+      <c r="D110" t="s">
+        <v>537</v>
+      </c>
+      <c r="E110" t="s">
+        <v>538</v>
+      </c>
+      <c r="F110" t="s">
         <v>539</v>
       </c>
-      <c r="B110" t="s">
+      <c r="G110" t="s">
         <v>540</v>
-      </c>
-      <c r="C110" t="s">
-        <v>541</v>
-      </c>
-      <c r="D110" t="s">
-        <v>542</v>
-      </c>
-      <c r="E110" t="s">
-        <v>543</v>
-      </c>
-      <c r="F110" t="s">
-        <v>544</v>
-      </c>
-      <c r="G110" t="s">
-        <v>545</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>539</v>
+        <v>534</v>
       </c>
       <c r="B111" t="s">
-        <v>546</v>
+        <v>541</v>
       </c>
       <c r="C111" t="s">
-        <v>547</v>
+        <v>542</v>
       </c>
       <c r="D111" t="s">
-        <v>548</v>
+        <v>543</v>
       </c>
       <c r="E111" t="s">
-        <v>543</v>
+        <v>538</v>
       </c>
       <c r="F111" t="s">
-        <v>549</v>
+        <v>544</v>
       </c>
       <c r="G111" t="s">
-        <v>545</v>
+        <v>540</v>
       </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>539</v>
+        <v>534</v>
       </c>
       <c r="B112" t="s">
-        <v>550</v>
+        <v>545</v>
       </c>
       <c r="C112" t="s">
-        <v>551</v>
+        <v>546</v>
       </c>
       <c r="D112" t="s">
-        <v>552</v>
+        <v>547</v>
       </c>
       <c r="E112" t="s">
-        <v>543</v>
+        <v>538</v>
       </c>
       <c r="F112" t="s">
-        <v>553</v>
+        <v>548</v>
       </c>
       <c r="G112" t="s">
-        <v>545</v>
+        <v>540</v>
       </c>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>539</v>
+        <v>534</v>
       </c>
       <c r="B113" t="s">
-        <v>554</v>
+        <v>549</v>
       </c>
       <c r="C113" t="s">
-        <v>555</v>
+        <v>550</v>
       </c>
       <c r="D113" t="s">
-        <v>556</v>
+        <v>551</v>
       </c>
       <c r="E113" t="s">
-        <v>543</v>
+        <v>538</v>
       </c>
       <c r="F113" t="s">
-        <v>557</v>
+        <v>552</v>
       </c>
       <c r="G113" t="s">
-        <v>545</v>
+        <v>540</v>
       </c>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>539</v>
+        <v>534</v>
       </c>
       <c r="B114" t="s">
-        <v>558</v>
+        <v>553</v>
       </c>
       <c r="C114" t="s">
-        <v>559</v>
+        <v>554</v>
       </c>
       <c r="D114" t="s">
-        <v>560</v>
+        <v>555</v>
       </c>
       <c r="E114" t="s">
-        <v>543</v>
+        <v>538</v>
       </c>
       <c r="F114" t="s">
-        <v>561</v>
+        <v>556</v>
       </c>
       <c r="G114" t="s">
-        <v>545</v>
+        <v>540</v>
       </c>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>539</v>
+        <v>534</v>
       </c>
       <c r="B115" t="s">
-        <v>562</v>
+        <v>557</v>
       </c>
       <c r="C115" t="s">
-        <v>563</v>
+        <v>558</v>
       </c>
       <c r="D115" t="s">
-        <v>564</v>
+        <v>559</v>
       </c>
       <c r="E115" t="s">
-        <v>543</v>
+        <v>538</v>
       </c>
       <c r="F115" t="s">
-        <v>565</v>
+        <v>560</v>
       </c>
       <c r="G115" t="s">
-        <v>545</v>
+        <v>540</v>
       </c>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>539</v>
+        <v>534</v>
       </c>
       <c r="B116" t="s">
-        <v>566</v>
+        <v>561</v>
       </c>
       <c r="C116" t="s">
-        <v>567</v>
+        <v>562</v>
       </c>
       <c r="D116" t="s">
-        <v>568</v>
+        <v>563</v>
       </c>
       <c r="E116" t="s">
-        <v>543</v>
+        <v>538</v>
       </c>
       <c r="F116" t="s">
-        <v>569</v>
+        <v>564</v>
       </c>
       <c r="G116" t="s">
-        <v>545</v>
+        <v>540</v>
       </c>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>539</v>
+        <v>534</v>
       </c>
       <c r="B117" t="s">
-        <v>570</v>
+        <v>565</v>
       </c>
       <c r="C117" t="s">
-        <v>571</v>
+        <v>566</v>
       </c>
       <c r="D117" t="s">
-        <v>572</v>
+        <v>567</v>
       </c>
       <c r="E117" t="s">
-        <v>543</v>
+        <v>538</v>
       </c>
       <c r="F117" t="s">
-        <v>573</v>
+        <v>568</v>
       </c>
       <c r="G117" t="s">
-        <v>545</v>
+        <v>540</v>
       </c>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>539</v>
+        <v>534</v>
       </c>
       <c r="B118" t="s">
-        <v>574</v>
+        <v>569</v>
       </c>
       <c r="C118" t="s">
-        <v>575</v>
+        <v>570</v>
       </c>
       <c r="D118" t="s">
-        <v>576</v>
+        <v>571</v>
       </c>
       <c r="E118" t="s">
-        <v>543</v>
+        <v>538</v>
       </c>
       <c r="F118" t="s">
-        <v>577</v>
+        <v>572</v>
       </c>
       <c r="G118" t="s">
-        <v>545</v>
+        <v>540</v>
       </c>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>539</v>
+        <v>534</v>
       </c>
       <c r="B119" t="s">
-        <v>578</v>
+        <v>573</v>
       </c>
       <c r="C119" t="s">
-        <v>579</v>
+        <v>574</v>
       </c>
       <c r="D119" t="s">
-        <v>580</v>
+        <v>575</v>
       </c>
       <c r="E119" t="s">
-        <v>543</v>
+        <v>538</v>
       </c>
       <c r="F119" t="s">
-        <v>581</v>
+        <v>576</v>
       </c>
       <c r="G119" t="s">
-        <v>545</v>
+        <v>540</v>
       </c>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>539</v>
+        <v>534</v>
       </c>
       <c r="B120" t="s">
-        <v>582</v>
+        <v>577</v>
       </c>
       <c r="C120" t="s">
-        <v>583</v>
+        <v>578</v>
       </c>
       <c r="D120" t="s">
-        <v>584</v>
+        <v>579</v>
       </c>
       <c r="E120" t="s">
-        <v>543</v>
+        <v>538</v>
       </c>
       <c r="F120" t="s">
-        <v>585</v>
+        <v>580</v>
       </c>
       <c r="G120" t="s">
-        <v>545</v>
+        <v>540</v>
       </c>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>539</v>
+        <v>534</v>
       </c>
       <c r="B121" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="C121" t="s">
-        <v>587</v>
+        <v>582</v>
       </c>
       <c r="D121" t="s">
-        <v>588</v>
+        <v>583</v>
       </c>
       <c r="E121" t="s">
-        <v>543</v>
+        <v>538</v>
       </c>
       <c r="F121" t="s">
-        <v>589</v>
+        <v>584</v>
       </c>
       <c r="G121" t="s">
-        <v>545</v>
+        <v>540</v>
       </c>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
+        <v>585</v>
+      </c>
+      <c r="B122" t="s">
+        <v>586</v>
+      </c>
+      <c r="C122" t="s">
+        <v>587</v>
+      </c>
+      <c r="D122" t="s">
+        <v>588</v>
+      </c>
+      <c r="E122" t="s">
+        <v>589</v>
+      </c>
+      <c r="F122" t="s">
         <v>590</v>
       </c>
-      <c r="B122" t="s">
+      <c r="G122" t="s">
         <v>591</v>
-      </c>
-      <c r="C122" t="s">
-        <v>592</v>
-      </c>
-      <c r="D122" t="s">
-        <v>593</v>
-      </c>
-      <c r="E122" t="s">
-        <v>594</v>
-      </c>
-      <c r="F122" t="s">
-        <v>595</v>
-      </c>
-      <c r="G122" t="s">
-        <v>596</v>
       </c>
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>590</v>
+        <v>585</v>
       </c>
       <c r="B123" t="s">
-        <v>597</v>
+        <v>592</v>
       </c>
       <c r="C123" t="s">
-        <v>598</v>
+        <v>593</v>
       </c>
       <c r="D123" t="s">
-        <v>599</v>
+        <v>594</v>
       </c>
       <c r="E123" t="s">
-        <v>594</v>
+        <v>589</v>
       </c>
       <c r="F123" t="s">
-        <v>600</v>
+        <v>595</v>
       </c>
       <c r="G123" t="s">
-        <v>596</v>
+        <v>591</v>
       </c>
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>590</v>
+        <v>585</v>
       </c>
       <c r="B124" t="s">
-        <v>601</v>
+        <v>596</v>
       </c>
       <c r="C124" t="s">
-        <v>602</v>
+        <v>597</v>
       </c>
       <c r="D124" t="s">
-        <v>603</v>
+        <v>598</v>
       </c>
       <c r="E124" t="s">
-        <v>594</v>
+        <v>589</v>
       </c>
       <c r="F124" t="s">
-        <v>604</v>
+        <v>599</v>
       </c>
       <c r="G124" t="s">
-        <v>596</v>
+        <v>591</v>
       </c>
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>590</v>
+        <v>585</v>
       </c>
       <c r="B125" t="s">
-        <v>605</v>
+        <v>600</v>
       </c>
       <c r="C125" t="s">
-        <v>606</v>
+        <v>601</v>
       </c>
       <c r="D125" t="s">
-        <v>607</v>
+        <v>602</v>
       </c>
       <c r="E125" t="s">
-        <v>594</v>
+        <v>589</v>
       </c>
       <c r="F125" t="s">
-        <v>608</v>
+        <v>603</v>
       </c>
       <c r="G125" t="s">
-        <v>596</v>
+        <v>591</v>
       </c>
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>590</v>
+        <v>585</v>
       </c>
       <c r="B126" t="s">
-        <v>609</v>
+        <v>604</v>
       </c>
       <c r="C126" t="s">
-        <v>610</v>
+        <v>605</v>
       </c>
       <c r="D126" t="s">
-        <v>611</v>
+        <v>606</v>
       </c>
       <c r="E126" t="s">
-        <v>594</v>
+        <v>589</v>
       </c>
       <c r="F126" t="s">
-        <v>612</v>
+        <v>607</v>
       </c>
       <c r="G126" t="s">
-        <v>596</v>
+        <v>591</v>
       </c>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>590</v>
+        <v>585</v>
       </c>
       <c r="B127" t="s">
-        <v>613</v>
+        <v>608</v>
       </c>
       <c r="C127" t="s">
-        <v>614</v>
+        <v>609</v>
       </c>
       <c r="D127" t="s">
-        <v>615</v>
+        <v>610</v>
       </c>
       <c r="E127" t="s">
-        <v>594</v>
+        <v>589</v>
       </c>
       <c r="F127" t="s">
-        <v>616</v>
+        <v>611</v>
       </c>
       <c r="G127" t="s">
-        <v>596</v>
+        <v>591</v>
       </c>
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>590</v>
+        <v>585</v>
       </c>
       <c r="B128" t="s">
-        <v>617</v>
+        <v>612</v>
       </c>
       <c r="C128" t="s">
-        <v>618</v>
+        <v>613</v>
       </c>
       <c r="D128" t="s">
-        <v>619</v>
+        <v>614</v>
       </c>
       <c r="E128" t="s">
-        <v>594</v>
+        <v>589</v>
       </c>
       <c r="F128" t="s">
-        <v>620</v>
+        <v>615</v>
       </c>
       <c r="G128" t="s">
-        <v>596</v>
+        <v>591</v>
       </c>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>590</v>
+        <v>585</v>
       </c>
       <c r="B129" t="s">
-        <v>621</v>
+        <v>616</v>
       </c>
       <c r="C129" t="s">
-        <v>622</v>
+        <v>617</v>
       </c>
       <c r="D129" t="s">
-        <v>623</v>
+        <v>618</v>
       </c>
       <c r="E129" t="s">
-        <v>594</v>
+        <v>589</v>
       </c>
       <c r="F129" t="s">
-        <v>624</v>
+        <v>619</v>
       </c>
       <c r="G129" t="s">
-        <v>596</v>
+        <v>591</v>
       </c>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>590</v>
+        <v>585</v>
       </c>
       <c r="B130" t="s">
-        <v>625</v>
+        <v>620</v>
       </c>
       <c r="C130" t="s">
-        <v>626</v>
+        <v>621</v>
       </c>
       <c r="D130" t="s">
-        <v>627</v>
+        <v>622</v>
       </c>
       <c r="E130" t="s">
-        <v>594</v>
+        <v>589</v>
       </c>
       <c r="F130" t="s">
-        <v>628</v>
+        <v>623</v>
       </c>
       <c r="G130" t="s">
-        <v>596</v>
+        <v>591</v>
       </c>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>590</v>
+        <v>585</v>
       </c>
       <c r="B131" t="s">
-        <v>629</v>
+        <v>624</v>
       </c>
       <c r="C131" t="s">
-        <v>630</v>
+        <v>625</v>
       </c>
       <c r="D131" t="s">
-        <v>631</v>
+        <v>626</v>
       </c>
       <c r="E131" t="s">
-        <v>594</v>
+        <v>589</v>
       </c>
       <c r="F131" t="s">
-        <v>632</v>
+        <v>627</v>
       </c>
       <c r="G131" t="s">
-        <v>596</v>
+        <v>591</v>
       </c>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
+        <v>628</v>
+      </c>
+      <c r="B132" t="s">
+        <v>629</v>
+      </c>
+      <c r="C132" t="s">
+        <v>630</v>
+      </c>
+      <c r="D132" t="s">
+        <v>631</v>
+      </c>
+      <c r="E132" t="s">
+        <v>632</v>
+      </c>
+      <c r="F132" t="s">
         <v>633</v>
       </c>
-      <c r="B132" t="s">
+      <c r="G132" t="s">
         <v>634</v>
-      </c>
-      <c r="C132" t="s">
-        <v>635</v>
-      </c>
-      <c r="D132" t="s">
-        <v>636</v>
-      </c>
-      <c r="E132" t="s">
-        <v>637</v>
-      </c>
-      <c r="F132" t="s">
-        <v>638</v>
-      </c>
-      <c r="G132" t="s">
-        <v>639</v>
       </c>
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>633</v>
+        <v>628</v>
       </c>
       <c r="B133" t="s">
-        <v>640</v>
+        <v>635</v>
       </c>
       <c r="C133" t="s">
-        <v>641</v>
+        <v>636</v>
       </c>
       <c r="D133" t="s">
-        <v>642</v>
+        <v>637</v>
       </c>
       <c r="E133" t="s">
-        <v>637</v>
+        <v>632</v>
       </c>
       <c r="F133" t="s">
-        <v>643</v>
+        <v>638</v>
       </c>
       <c r="G133" t="s">
-        <v>639</v>
+        <v>634</v>
       </c>
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>633</v>
+        <v>628</v>
       </c>
       <c r="B134" t="s">
-        <v>644</v>
+        <v>639</v>
       </c>
       <c r="C134" t="s">
-        <v>645</v>
+        <v>640</v>
       </c>
       <c r="D134" t="s">
-        <v>646</v>
+        <v>641</v>
       </c>
       <c r="E134" t="s">
-        <v>637</v>
+        <v>632</v>
       </c>
       <c r="F134" t="s">
-        <v>647</v>
+        <v>642</v>
       </c>
       <c r="G134" t="s">
-        <v>639</v>
+        <v>634</v>
       </c>
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>633</v>
+        <v>628</v>
       </c>
       <c r="B135" t="s">
-        <v>648</v>
+        <v>643</v>
       </c>
       <c r="C135" t="s">
-        <v>649</v>
+        <v>644</v>
       </c>
       <c r="D135" t="s">
-        <v>650</v>
+        <v>645</v>
       </c>
       <c r="E135" t="s">
-        <v>637</v>
+        <v>632</v>
       </c>
       <c r="F135" t="s">
-        <v>651</v>
+        <v>646</v>
       </c>
       <c r="G135" t="s">
-        <v>639</v>
+        <v>634</v>
       </c>
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>633</v>
+        <v>628</v>
       </c>
       <c r="B136" t="s">
-        <v>652</v>
+        <v>647</v>
       </c>
       <c r="C136" t="s">
-        <v>653</v>
+        <v>648</v>
       </c>
       <c r="D136" t="s">
-        <v>654</v>
+        <v>649</v>
       </c>
       <c r="E136" t="s">
-        <v>637</v>
+        <v>632</v>
       </c>
       <c r="F136" t="s">
-        <v>655</v>
+        <v>650</v>
       </c>
       <c r="G136" t="s">
-        <v>639</v>
+        <v>634</v>
       </c>
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>633</v>
+        <v>628</v>
       </c>
       <c r="B137" t="s">
-        <v>656</v>
+        <v>651</v>
       </c>
       <c r="C137" t="s">
-        <v>657</v>
+        <v>652</v>
       </c>
       <c r="D137" t="s">
-        <v>658</v>
+        <v>653</v>
       </c>
       <c r="E137" t="s">
-        <v>637</v>
+        <v>632</v>
       </c>
       <c r="F137" t="s">
-        <v>659</v>
+        <v>654</v>
       </c>
       <c r="G137" t="s">
-        <v>639</v>
+        <v>634</v>
       </c>
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>633</v>
+        <v>628</v>
       </c>
       <c r="B138" t="s">
-        <v>660</v>
+        <v>655</v>
       </c>
       <c r="C138" t="s">
-        <v>661</v>
+        <v>656</v>
       </c>
       <c r="D138" t="s">
-        <v>662</v>
+        <v>657</v>
       </c>
       <c r="E138" t="s">
-        <v>637</v>
+        <v>632</v>
       </c>
       <c r="F138" t="s">
-        <v>663</v>
+        <v>658</v>
       </c>
       <c r="G138" t="s">
-        <v>639</v>
+        <v>634</v>
       </c>
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>633</v>
+        <v>628</v>
       </c>
       <c r="B139" t="s">
-        <v>664</v>
+        <v>659</v>
       </c>
       <c r="C139" t="s">
-        <v>665</v>
+        <v>660</v>
       </c>
       <c r="D139" t="s">
-        <v>666</v>
+        <v>661</v>
       </c>
       <c r="E139" t="s">
-        <v>637</v>
+        <v>632</v>
       </c>
       <c r="F139" t="s">
-        <v>667</v>
+        <v>662</v>
       </c>
       <c r="G139" t="s">
-        <v>639</v>
+        <v>634</v>
       </c>
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>633</v>
+        <v>628</v>
       </c>
       <c r="B140" t="s">
-        <v>668</v>
+        <v>663</v>
       </c>
       <c r="C140" t="s">
-        <v>669</v>
+        <v>664</v>
       </c>
       <c r="D140" t="s">
-        <v>670</v>
+        <v>665</v>
       </c>
       <c r="E140" t="s">
-        <v>637</v>
+        <v>632</v>
       </c>
       <c r="F140" t="s">
-        <v>671</v>
+        <v>666</v>
       </c>
       <c r="G140" t="s">
-        <v>639</v>
+        <v>634</v>
       </c>
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>633</v>
+        <v>628</v>
       </c>
       <c r="B141" t="s">
-        <v>672</v>
+        <v>667</v>
       </c>
       <c r="C141" t="s">
-        <v>673</v>
+        <v>668</v>
       </c>
       <c r="D141" t="s">
-        <v>674</v>
+        <v>669</v>
       </c>
       <c r="E141" t="s">
-        <v>637</v>
+        <v>632</v>
       </c>
       <c r="F141" t="s">
-        <v>675</v>
+        <v>670</v>
       </c>
       <c r="G141" t="s">
-        <v>639</v>
+        <v>634</v>
       </c>
     </row>
   </sheetData>
